--- a/data/inflation.xlsx
+++ b/data/inflation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Real estate Forecast\RealEstateAI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Real estate Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4605D215-FBA7-4CC9-8F2F-60C13CF57DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946D39D0-CF87-4C55-B5A3-A076C211A460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C3F75CC-EF30-4873-A10D-A4A6E40F37D9}"/>
+    <workbookView xWindow="31200" yWindow="2400" windowWidth="22575" windowHeight="13290" xr2:uid="{9C3F75CC-EF30-4873-A10D-A4A6E40F37D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -82,6 +82,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -99,7 +105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -107,6 +113,9 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE5A24B-9BEA-4A64-B1BB-17BC1CC0E751}">
-  <dimension ref="A1:D197"/>
+  <dimension ref="A1:D202"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -3199,7 +3208,7 @@
       <c r="B196" s="4">
         <v>3.3</v>
       </c>
-      <c r="C196" s="6">
+      <c r="C196" s="3">
         <v>4.3</v>
       </c>
       <c r="D196">
@@ -3213,11 +3222,81 @@
       <c r="B197" s="4">
         <v>3.5</v>
       </c>
-      <c r="C197" s="6">
+      <c r="C197" s="3">
         <v>4.4000000000000004</v>
       </c>
       <c r="D197">
         <v>49.8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B198" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="C198" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="D198">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B199" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="C199" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="D199">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B200" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="C200" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D200">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B201" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="C201" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D201">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" s="7">
+        <v>46266</v>
+      </c>
+      <c r="B202" s="8">
+        <v>3.57</v>
+      </c>
+      <c r="C202" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D202" s="8">
+        <v>48.1</v>
       </c>
     </row>
   </sheetData>
